--- a/docs/paper/eric_lychee_paper_submission.xlsx
+++ b/docs/paper/eric_lychee_paper_submission.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rzhuang/Documents/VscodeProjects/lychee/docs/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E04BF8F-D8A4-F84F-9642-410EE70C3992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691C81CA-406E-3F41-93A5-5AF834560746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="660" windowWidth="33560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="4420" windowWidth="26500" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="1" r:id="rId1"/>
-    <sheet name="Paper" sheetId="2" r:id="rId2"/>
-    <sheet name="Conference" sheetId="3" r:id="rId3"/>
+    <sheet name="journal" sheetId="2" r:id="rId2"/>
+    <sheet name="conference" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
   <si>
     <t>https://zenodo.org/records/22240717</t>
   </si>
@@ -227,12 +227,21 @@
   <si>
     <t>v2</t>
   </si>
+  <si>
+    <t>Plant Protection Science</t>
+  </si>
+  <si>
+    <t>https://pps.agriculturejournals.cz/</t>
+  </si>
+  <si>
+    <t>ericzhuang2010 HappyKids2026!!!</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -311,6 +320,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFBBBEBF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial (Body)"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -333,7 +355,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -357,6 +379,8 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -598,7 +622,7 @@
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" t="s">
+      <c r="B5" s="13" t="s">
         <v>17</v>
       </c>
     </row>
@@ -743,6 +767,9 @@
       <c r="E5" s="9">
         <v>1.1000000000000001</v>
       </c>
+      <c r="F5" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="G5">
         <v>2</v>
       </c>
@@ -781,15 +808,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="8"/>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="10"/>
+    <row r="8" spans="1:23" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="11">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="8"/>
       <c r="E9" s="9"/>
     </row>
@@ -831,7 +869,7 @@
       <c r="A13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -3871,6 +3909,7 @@
     <hyperlink ref="B16" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
     <hyperlink ref="B17" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
     <hyperlink ref="B18" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="B8" r:id="rId12" xr:uid="{E43F01E8-3011-894B-8F4A-41DD87D3B8CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/paper/eric_lychee_paper_submission.xlsx
+++ b/docs/paper/eric_lychee_paper_submission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rzhuang/Documents/VscodeProjects/lychee/docs/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691C81CA-406E-3F41-93A5-5AF834560746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7CC449-9033-B44B-AFA1-6000F250F5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="4420" windowWidth="26500" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1060" yWindow="660" windowWidth="33500" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
   <si>
     <t>https://zenodo.org/records/22240717</t>
   </si>
@@ -235,6 +235,15 @@
   </si>
   <si>
     <t>ericzhuang2010 HappyKids2026!!!</t>
+  </si>
+  <si>
+    <t>https://www.editorialmanager.com/pone/Default.aspx</t>
+  </si>
+  <si>
+    <t>ericzhuang2010 Rocket123#######</t>
+  </si>
+  <si>
+    <t>MDPI plants</t>
   </si>
 </sst>
 </file>
@@ -646,7 +655,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1004"/>
+  <dimension ref="A1:W1005"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="11" customWidth="1"/>
@@ -826,7 +835,9 @@
       </c>
     </row>
     <row r="9" spans="1:23" ht="18" x14ac:dyDescent="0.2">
-      <c r="A9" s="14"/>
+      <c r="A9" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="B9" s="15"/>
       <c r="C9" s="8"/>
       <c r="E9" s="9"/>
@@ -865,81 +876,90 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" spans="1:23" ht="29" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E14" s="9">
         <v>2.8</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+    <row r="15" spans="1:23" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B15" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E15" s="9">
         <v>2.4</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="51" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
+    <row r="17" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B17" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E17" s="9">
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="85" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
+    <row r="18" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E18" s="9">
         <v>5.9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+    <row r="19" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B19" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E19" s="9">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
@@ -3895,6 +3915,9 @@
     </row>
     <row r="1004" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1004" s="8"/>
+    </row>
+    <row r="1005" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1005" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3904,12 +3927,13 @@
     <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
     <hyperlink ref="B11" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
     <hyperlink ref="B12" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="B13" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="B14" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="B16" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="B17" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="B18" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="B8" r:id="rId12" xr:uid="{E43F01E8-3011-894B-8F4A-41DD87D3B8CC}"/>
+    <hyperlink ref="B17" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="B18" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="B19" r:id="rId9" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="B8" r:id="rId10" xr:uid="{E43F01E8-3011-894B-8F4A-41DD87D3B8CC}"/>
+    <hyperlink ref="C14" r:id="rId11" xr:uid="{79E265A6-6F6A-8F49-AA93-06B0B974AF45}"/>
+    <hyperlink ref="B15" r:id="rId12" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/paper/eric_lychee_paper_submission.xlsx
+++ b/docs/paper/eric_lychee_paper_submission.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rzhuang/Documents/VscodeProjects/lychee/docs/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7CC449-9033-B44B-AFA1-6000F250F5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8E2BBE-BC3F-D74E-AA74-7DF53E6DF10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="660" windowWidth="33500" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>https://zenodo.org/records/22240717</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>MDPI plants</t>
+  </si>
+  <si>
+    <t>revised and submitted</t>
   </si>
 </sst>
 </file>
@@ -663,7 +666,7 @@
     <col min="3" max="3" width="21.1640625" style="11" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="11" customWidth="1"/>
     <col min="5" max="5" width="7.83203125" style="11" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="11"/>
+    <col min="6" max="6" width="22.33203125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16" x14ac:dyDescent="0.2">
@@ -830,8 +833,11 @@
       <c r="E8" s="11">
         <v>1</v>
       </c>
+      <c r="F8" s="11" t="s">
+        <v>71</v>
+      </c>
       <c r="G8">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="18" x14ac:dyDescent="0.2">
